--- a/import/Корректировки/3 неделя/15.09.xlsx
+++ b/import/Корректировки/3 неделя/15.09.xlsx
@@ -159,7 +159,7 @@
     <t>Эконом.отр.</t>
   </si>
   <si>
-    <t>Кобзеренко Л.Н.</t>
+    <t>Кобзаренко Л.Н.</t>
   </si>
   <si>
     <t>Москаленко М.А.</t>
